--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:22</t>
+    <t xml:space="preserve">2026-09-09 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:19</t>
+    <t xml:space="preserve">2026-09-17 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:14</t>
+    <t xml:space="preserve">2026-09-23 12:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:43</t>
+    <t xml:space="preserve">2026-10-02 14:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:56</t>
+    <t xml:space="preserve">2026-10-05 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
